--- a/registration_forms/016_graduation_cap_and_gown_order_form--registration_forms.xlsx
+++ b/registration_forms/016_graduation_cap_and_gown_order_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cap Size</t>
+          <t>Graduation Cap Size</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tassel Color</t>
+          <t>Graduation Tassel Color Type</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gown Type</t>
+          <t>Graduation Gown Type</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>graduation_order_status</t>
+          <t>graduation_order_status_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Graduation Order Status</t>
+          <t>Graduation Order Status 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1738,7 +1738,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>graduation_order_status_choices</t>
+          <t>graduation_order_status_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>graduation_order_status_choices</t>
+          <t>graduation_order_status_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1772,7 +1772,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>graduation_order_status_choices</t>
+          <t>graduation_order_status_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
